--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -1079,7 +1079,7 @@
         <v>131066787</v>
       </c>
       <c r="B6" t="n">
-        <v>80385</v>
+        <v>80386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066771</v>
+        <v>131066788</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>83218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,42 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425297</v>
+        <v>425211</v>
       </c>
       <c r="R7" t="n">
-        <v>6712214</v>
+        <v>6712276</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1252,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066788</v>
+        <v>131066771</v>
       </c>
       <c r="B8" t="n">
-        <v>83217</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,34 +1281,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425211</v>
+        <v>425297</v>
       </c>
       <c r="R8" t="n">
-        <v>6712276</v>
+        <v>6712214</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131066783</v>
+        <v>131066770</v>
       </c>
       <c r="B9" t="n">
-        <v>83091</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1391,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425170</v>
+        <v>425323</v>
       </c>
       <c r="R9" t="n">
-        <v>6712292</v>
+        <v>6712206</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1451,6 +1459,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131066770</v>
+        <v>131066783</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>83092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,42 +1501,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425323</v>
+        <v>425170</v>
       </c>
       <c r="R10" t="n">
-        <v>6712206</v>
+        <v>6712292</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1556,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,7 +1590,7 @@
         <v>131066760</v>
       </c>
       <c r="B11" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>131066781</v>
       </c>
       <c r="B12" t="n">
-        <v>83208</v>
+        <v>83209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131066780</v>
       </c>
       <c r="B13" t="n">
-        <v>83208</v>
+        <v>83209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131066792</v>
       </c>
       <c r="B14" t="n">
-        <v>83217</v>
+        <v>83218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>131066761</v>
       </c>
       <c r="B15" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>131066782</v>
       </c>
       <c r="B16" t="n">
-        <v>91827</v>
+        <v>91828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>131066768</v>
       </c>
       <c r="B17" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2596,32 +2596,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066778</v>
+        <v>131066766</v>
       </c>
       <c r="B21" t="n">
-        <v>81230</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425336</v>
+        <v>425069</v>
       </c>
       <c r="R21" t="n">
-        <v>6712202</v>
+        <v>6712285</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131066774</v>
+        <v>131066778</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>81231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2704,42 +2704,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425250</v>
+        <v>425336</v>
       </c>
       <c r="R22" t="n">
-        <v>6712265</v>
+        <v>6712202</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2772,11 +2764,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2803,45 +2790,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131066766</v>
+        <v>131066774</v>
       </c>
       <c r="B23" t="n">
-        <v>92184</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425069</v>
+        <v>425250</v>
       </c>
       <c r="R23" t="n">
-        <v>6712285</v>
+        <v>6712265</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2874,6 +2869,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2903,7 +2903,7 @@
         <v>131066786</v>
       </c>
       <c r="B24" t="n">
-        <v>83091</v>
+        <v>83092</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>131066762</v>
       </c>
       <c r="B25" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131066765</v>
       </c>
       <c r="B26" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>131066789</v>
       </c>
       <c r="B27" t="n">
-        <v>83217</v>
+        <v>83218</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131066791</v>
       </c>
       <c r="B28" t="n">
-        <v>83217</v>
+        <v>83218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131066777</v>
       </c>
       <c r="B29" t="n">
-        <v>92232</v>
+        <v>92233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131066772</v>
+        <v>131066776</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>80352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,42 +3494,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425301</v>
+        <v>425069</v>
       </c>
       <c r="R30" t="n">
-        <v>6712219</v>
+        <v>6712285</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3562,11 +3554,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3593,10 +3580,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131066776</v>
+        <v>131066772</v>
       </c>
       <c r="B31" t="n">
-        <v>80351</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3604,34 +3591,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425069</v>
+        <v>425301</v>
       </c>
       <c r="R31" t="n">
-        <v>6712285</v>
+        <v>6712219</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3664,6 +3659,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3693,7 +3693,7 @@
         <v>131066767</v>
       </c>
       <c r="B32" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>131066790</v>
       </c>
       <c r="B33" t="n">
-        <v>83217</v>
+        <v>83218</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>131066784</v>
       </c>
       <c r="B34" t="n">
-        <v>83091</v>
+        <v>83092</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -2072,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066782</v>
+        <v>131066769</v>
       </c>
       <c r="B16" t="n">
-        <v>91828</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,34 +2083,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425059</v>
+        <v>425267</v>
       </c>
       <c r="R16" t="n">
-        <v>6712253</v>
+        <v>6712232</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2143,6 +2151,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2169,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066768</v>
+        <v>131066782</v>
       </c>
       <c r="B17" t="n">
-        <v>91814</v>
+        <v>91828</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2180,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2204,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425256</v>
+        <v>425059</v>
       </c>
       <c r="R17" t="n">
-        <v>6712203</v>
+        <v>6712253</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2266,10 +2279,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131066769</v>
+        <v>131066768</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,42 +2290,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425267</v>
+        <v>425256</v>
       </c>
       <c r="R18" t="n">
-        <v>6712232</v>
+        <v>6712203</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2345,11 +2350,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -1076,45 +1076,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066787</v>
+        <v>131066771</v>
       </c>
       <c r="B6" t="n">
-        <v>80386</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425069</v>
+        <v>425297</v>
       </c>
       <c r="R6" t="n">
-        <v>6712290</v>
+        <v>6712214</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1147,6 +1155,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,32 +1186,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066788</v>
+        <v>131066787</v>
       </c>
       <c r="B7" t="n">
-        <v>83218</v>
+        <v>80388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425211</v>
+        <v>425069</v>
       </c>
       <c r="R7" t="n">
-        <v>6712276</v>
+        <v>6712290</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1270,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066771</v>
+        <v>131066788</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>83220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,42 +1294,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425297</v>
+        <v>425211</v>
       </c>
       <c r="R8" t="n">
-        <v>6712214</v>
+        <v>6712276</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1349,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131066770</v>
+        <v>131066783</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>83094</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,42 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425323</v>
+        <v>425170</v>
       </c>
       <c r="R9" t="n">
-        <v>6712206</v>
+        <v>6712292</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1459,11 +1451,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131066783</v>
+        <v>131066770</v>
       </c>
       <c r="B10" t="n">
-        <v>83092</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,34 +1488,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425170</v>
+        <v>425323</v>
       </c>
       <c r="R10" t="n">
-        <v>6712292</v>
+        <v>6712206</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1561,6 +1556,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,7 +1590,7 @@
         <v>131066760</v>
       </c>
       <c r="B11" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>131066781</v>
       </c>
       <c r="B12" t="n">
-        <v>83209</v>
+        <v>83211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131066780</v>
       </c>
       <c r="B13" t="n">
-        <v>83209</v>
+        <v>83211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131066792</v>
       </c>
       <c r="B14" t="n">
-        <v>83218</v>
+        <v>83220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,45 +1975,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131066761</v>
+        <v>131066769</v>
       </c>
       <c r="B15" t="n">
-        <v>91777</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425072</v>
+        <v>425267</v>
       </c>
       <c r="R15" t="n">
-        <v>6712273</v>
+        <v>6712232</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2046,6 +2054,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2072,53 +2085,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066769</v>
+        <v>131066761</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>91779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425267</v>
+        <v>425072</v>
       </c>
       <c r="R16" t="n">
-        <v>6712232</v>
+        <v>6712273</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2151,11 +2156,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066782</v>
+        <v>131066768</v>
       </c>
       <c r="B17" t="n">
-        <v>91828</v>
+        <v>91816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425059</v>
+        <v>425256</v>
       </c>
       <c r="R17" t="n">
-        <v>6712253</v>
+        <v>6712203</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2279,10 +2279,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131066768</v>
+        <v>131066782</v>
       </c>
       <c r="B18" t="n">
-        <v>91814</v>
+        <v>91830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2290,21 +2290,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425256</v>
+        <v>425059</v>
       </c>
       <c r="R18" t="n">
-        <v>6712203</v>
+        <v>6712253</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2379,7 +2379,7 @@
         <v>131066775</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>131066773</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,32 +2596,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066766</v>
+        <v>131066778</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>81233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425069</v>
+        <v>425336</v>
       </c>
       <c r="R21" t="n">
-        <v>6712285</v>
+        <v>6712202</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2693,32 +2693,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131066778</v>
+        <v>131066766</v>
       </c>
       <c r="B22" t="n">
-        <v>81231</v>
+        <v>92187</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425336</v>
+        <v>425069</v>
       </c>
       <c r="R22" t="n">
-        <v>6712202</v>
+        <v>6712285</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2793,7 +2793,7 @@
         <v>131066774</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>131066786</v>
       </c>
       <c r="B24" t="n">
-        <v>83092</v>
+        <v>83094</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>131066762</v>
       </c>
       <c r="B25" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131066765</v>
       </c>
       <c r="B26" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>131066789</v>
       </c>
       <c r="B27" t="n">
-        <v>83218</v>
+        <v>83220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131066791</v>
       </c>
       <c r="B28" t="n">
-        <v>83218</v>
+        <v>83220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131066777</v>
       </c>
       <c r="B29" t="n">
-        <v>92233</v>
+        <v>92235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>131066776</v>
       </c>
       <c r="B30" t="n">
-        <v>80352</v>
+        <v>80354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>131066772</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131066767</v>
+        <v>131066784</v>
       </c>
       <c r="B32" t="n">
-        <v>91814</v>
+        <v>83094</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425259</v>
+        <v>425170</v>
       </c>
       <c r="R32" t="n">
-        <v>6712201</v>
+        <v>6712283</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3790,7 +3790,7 @@
         <v>131066790</v>
       </c>
       <c r="B33" t="n">
-        <v>83218</v>
+        <v>83220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131066784</v>
+        <v>131066767</v>
       </c>
       <c r="B34" t="n">
-        <v>83092</v>
+        <v>91816</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425170</v>
+        <v>425259</v>
       </c>
       <c r="R34" t="n">
-        <v>6712283</v>
+        <v>6712201</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066771</v>
+        <v>131066788</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>83221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,42 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425297</v>
+        <v>425211</v>
       </c>
       <c r="R6" t="n">
-        <v>6712214</v>
+        <v>6712276</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1155,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,7 +1176,7 @@
         <v>131066787</v>
       </c>
       <c r="B7" t="n">
-        <v>80388</v>
+        <v>80389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066788</v>
+        <v>131066771</v>
       </c>
       <c r="B8" t="n">
-        <v>83220</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,34 +1281,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425211</v>
+        <v>425297</v>
       </c>
       <c r="R8" t="n">
-        <v>6712276</v>
+        <v>6712214</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1383,7 +1383,7 @@
         <v>131066783</v>
       </c>
       <c r="B9" t="n">
-        <v>83094</v>
+        <v>83095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131066770</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131066760</v>
       </c>
       <c r="B11" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>131066781</v>
       </c>
       <c r="B12" t="n">
-        <v>83211</v>
+        <v>83212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131066780</v>
       </c>
       <c r="B13" t="n">
-        <v>83211</v>
+        <v>83212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131066792</v>
       </c>
       <c r="B14" t="n">
-        <v>83220</v>
+        <v>83221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>131066769</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,32 +2085,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066761</v>
+        <v>131066782</v>
       </c>
       <c r="B16" t="n">
-        <v>91779</v>
+        <v>91831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425072</v>
+        <v>425059</v>
       </c>
       <c r="R16" t="n">
-        <v>6712273</v>
+        <v>6712253</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2185,7 +2185,7 @@
         <v>131066768</v>
       </c>
       <c r="B17" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,32 +2279,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131066782</v>
+        <v>131066761</v>
       </c>
       <c r="B18" t="n">
-        <v>91830</v>
+        <v>91780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425059</v>
+        <v>425072</v>
       </c>
       <c r="R18" t="n">
-        <v>6712253</v>
+        <v>6712273</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2379,7 +2379,7 @@
         <v>131066775</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>131066773</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066778</v>
+        <v>131066774</v>
       </c>
       <c r="B21" t="n">
-        <v>81233</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,34 +2607,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425336</v>
+        <v>425250</v>
       </c>
       <c r="R21" t="n">
-        <v>6712202</v>
+        <v>6712265</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2667,6 +2675,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2696,7 +2709,7 @@
         <v>131066766</v>
       </c>
       <c r="B22" t="n">
-        <v>92187</v>
+        <v>92188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,10 +2803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131066774</v>
+        <v>131066778</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>81234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2801,42 +2814,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425250</v>
+        <v>425336</v>
       </c>
       <c r="R23" t="n">
-        <v>6712265</v>
+        <v>6712202</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2869,11 +2874,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2903,7 +2903,7 @@
         <v>131066786</v>
       </c>
       <c r="B24" t="n">
-        <v>83094</v>
+        <v>83095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>131066762</v>
       </c>
       <c r="B25" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131066765</v>
       </c>
       <c r="B26" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>131066789</v>
       </c>
       <c r="B27" t="n">
-        <v>83220</v>
+        <v>83221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131066791</v>
       </c>
       <c r="B28" t="n">
-        <v>83220</v>
+        <v>83221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131066777</v>
       </c>
       <c r="B29" t="n">
-        <v>92235</v>
+        <v>92236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>131066776</v>
       </c>
       <c r="B30" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>131066772</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131066784</v>
+        <v>131066767</v>
       </c>
       <c r="B32" t="n">
-        <v>83094</v>
+        <v>91817</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425170</v>
+        <v>425259</v>
       </c>
       <c r="R32" t="n">
-        <v>6712283</v>
+        <v>6712201</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3790,7 +3790,7 @@
         <v>131066790</v>
       </c>
       <c r="B33" t="n">
-        <v>83220</v>
+        <v>83221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131066767</v>
+        <v>131066784</v>
       </c>
       <c r="B34" t="n">
-        <v>91816</v>
+        <v>83095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425259</v>
+        <v>425170</v>
       </c>
       <c r="R34" t="n">
-        <v>6712201</v>
+        <v>6712283</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066788</v>
+        <v>131066787</v>
       </c>
       <c r="B6" t="n">
-        <v>83221</v>
+        <v>80389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425211</v>
+        <v>425069</v>
       </c>
       <c r="R6" t="n">
-        <v>6712276</v>
+        <v>6712290</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1173,45 +1173,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066787</v>
+        <v>131066771</v>
       </c>
       <c r="B7" t="n">
-        <v>80389</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425069</v>
+        <v>425297</v>
       </c>
       <c r="R7" t="n">
-        <v>6712290</v>
+        <v>6712214</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1244,6 +1252,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066771</v>
+        <v>131066788</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>83221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,42 +1294,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425297</v>
+        <v>425211</v>
       </c>
       <c r="R8" t="n">
-        <v>6712214</v>
+        <v>6712276</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1349,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1975,10 +1975,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131066769</v>
+        <v>131066782</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>91831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,42 +1986,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425267</v>
+        <v>425059</v>
       </c>
       <c r="R15" t="n">
-        <v>6712232</v>
+        <v>6712253</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2054,11 +2046,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2085,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066782</v>
+        <v>131066768</v>
       </c>
       <c r="B16" t="n">
-        <v>91831</v>
+        <v>91817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2096,21 +2083,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2120,10 +2107,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425059</v>
+        <v>425256</v>
       </c>
       <c r="R16" t="n">
-        <v>6712253</v>
+        <v>6712203</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2182,10 +2169,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066768</v>
+        <v>131066769</v>
       </c>
       <c r="B17" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,34 +2180,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425256</v>
+        <v>425267</v>
       </c>
       <c r="R17" t="n">
-        <v>6712203</v>
+        <v>6712232</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2253,6 +2248,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,7 +2376,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131066775</v>
+        <v>131066773</v>
       </c>
       <c r="B19" t="n">
         <v>57887</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425244</v>
+        <v>425271</v>
       </c>
       <c r="R19" t="n">
-        <v>6712292</v>
+        <v>6712264</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131066773</v>
+        <v>131066775</v>
       </c>
       <c r="B20" t="n">
         <v>57887</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425271</v>
+        <v>425244</v>
       </c>
       <c r="R20" t="n">
-        <v>6712264</v>
+        <v>6712292</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2596,53 +2596,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066774</v>
+        <v>131066766</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>92188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425250</v>
+        <v>425069</v>
       </c>
       <c r="R21" t="n">
-        <v>6712265</v>
+        <v>6712285</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2675,11 +2667,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2706,32 +2693,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131066766</v>
+        <v>131066778</v>
       </c>
       <c r="B22" t="n">
-        <v>92188</v>
+        <v>81234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,10 +2728,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425069</v>
+        <v>425336</v>
       </c>
       <c r="R22" t="n">
-        <v>6712285</v>
+        <v>6712202</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2803,10 +2790,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131066778</v>
+        <v>131066774</v>
       </c>
       <c r="B23" t="n">
-        <v>81234</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,34 +2801,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425336</v>
+        <v>425250</v>
       </c>
       <c r="R23" t="n">
-        <v>6712202</v>
+        <v>6712265</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2874,6 +2869,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131066767</v>
+        <v>131066790</v>
       </c>
       <c r="B32" t="n">
-        <v>91817</v>
+        <v>83221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425259</v>
+        <v>425164</v>
       </c>
       <c r="R32" t="n">
-        <v>6712201</v>
+        <v>6712278</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131066790</v>
+        <v>131066767</v>
       </c>
       <c r="B33" t="n">
-        <v>83221</v>
+        <v>91817</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425164</v>
+        <v>425259</v>
       </c>
       <c r="R33" t="n">
-        <v>6712278</v>
+        <v>6712201</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066787</v>
+        <v>131066788</v>
       </c>
       <c r="B6" t="n">
-        <v>80389</v>
+        <v>83221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425069</v>
+        <v>425211</v>
       </c>
       <c r="R6" t="n">
-        <v>6712290</v>
+        <v>6712276</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1173,53 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066771</v>
+        <v>131066787</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>80389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425297</v>
+        <v>425069</v>
       </c>
       <c r="R7" t="n">
-        <v>6712214</v>
+        <v>6712290</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1252,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066788</v>
+        <v>131066771</v>
       </c>
       <c r="B8" t="n">
-        <v>83221</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,34 +1281,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425211</v>
+        <v>425297</v>
       </c>
       <c r="R8" t="n">
-        <v>6712276</v>
+        <v>6712214</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1975,32 +1975,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131066782</v>
+        <v>131066761</v>
       </c>
       <c r="B15" t="n">
-        <v>91831</v>
+        <v>91780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425059</v>
+        <v>425072</v>
       </c>
       <c r="R15" t="n">
-        <v>6712253</v>
+        <v>6712273</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066768</v>
+        <v>131066769</v>
       </c>
       <c r="B16" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,34 +2083,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425256</v>
+        <v>425267</v>
       </c>
       <c r="R16" t="n">
-        <v>6712203</v>
+        <v>6712232</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2143,6 +2151,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2169,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066769</v>
+        <v>131066782</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>91831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2180,42 +2193,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425267</v>
+        <v>425059</v>
       </c>
       <c r="R17" t="n">
-        <v>6712232</v>
+        <v>6712253</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2248,11 +2253,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2279,32 +2279,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131066761</v>
+        <v>131066768</v>
       </c>
       <c r="B18" t="n">
-        <v>91780</v>
+        <v>91817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425072</v>
+        <v>425256</v>
       </c>
       <c r="R18" t="n">
-        <v>6712273</v>
+        <v>6712203</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131066773</v>
+        <v>131066775</v>
       </c>
       <c r="B19" t="n">
         <v>57887</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425271</v>
+        <v>425244</v>
       </c>
       <c r="R19" t="n">
-        <v>6712264</v>
+        <v>6712292</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131066775</v>
+        <v>131066773</v>
       </c>
       <c r="B20" t="n">
         <v>57887</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425244</v>
+        <v>425271</v>
       </c>
       <c r="R20" t="n">
-        <v>6712292</v>
+        <v>6712264</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2596,45 +2596,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066766</v>
+        <v>131066774</v>
       </c>
       <c r="B21" t="n">
-        <v>92188</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425069</v>
+        <v>425250</v>
       </c>
       <c r="R21" t="n">
-        <v>6712285</v>
+        <v>6712265</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2667,6 +2675,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2693,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131066778</v>
+        <v>131066766</v>
       </c>
       <c r="B22" t="n">
-        <v>81234</v>
+        <v>92188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2741,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425336</v>
+        <v>425069</v>
       </c>
       <c r="R22" t="n">
-        <v>6712202</v>
+        <v>6712285</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2790,10 +2803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131066774</v>
+        <v>131066778</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>81234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2801,42 +2814,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425250</v>
+        <v>425336</v>
       </c>
       <c r="R23" t="n">
-        <v>6712265</v>
+        <v>6712202</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2869,11 +2874,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066788</v>
+        <v>131066771</v>
       </c>
       <c r="B6" t="n">
-        <v>83221</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425211</v>
+        <v>425297</v>
       </c>
       <c r="R6" t="n">
-        <v>6712276</v>
+        <v>6712214</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1147,6 +1155,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,32 +1186,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066787</v>
+        <v>131066788</v>
       </c>
       <c r="B7" t="n">
-        <v>80389</v>
+        <v>83222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425069</v>
+        <v>425211</v>
       </c>
       <c r="R7" t="n">
-        <v>6712290</v>
+        <v>6712276</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1270,53 +1283,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066771</v>
+        <v>131066787</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>80390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425297</v>
+        <v>425069</v>
       </c>
       <c r="R8" t="n">
-        <v>6712214</v>
+        <v>6712290</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1349,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131066783</v>
+        <v>131066770</v>
       </c>
       <c r="B9" t="n">
-        <v>83095</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1391,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425170</v>
+        <v>425323</v>
       </c>
       <c r="R9" t="n">
-        <v>6712292</v>
+        <v>6712206</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1451,6 +1459,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131066770</v>
+        <v>131066783</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>83096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,42 +1501,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425323</v>
+        <v>425170</v>
       </c>
       <c r="R10" t="n">
-        <v>6712206</v>
+        <v>6712292</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1556,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,7 +1590,7 @@
         <v>131066760</v>
       </c>
       <c r="B11" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>131066781</v>
       </c>
       <c r="B12" t="n">
-        <v>83212</v>
+        <v>83213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>131066780</v>
       </c>
       <c r="B13" t="n">
-        <v>83212</v>
+        <v>83213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131066792</v>
       </c>
       <c r="B14" t="n">
-        <v>83221</v>
+        <v>83222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,32 +1975,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131066761</v>
+        <v>131066768</v>
       </c>
       <c r="B15" t="n">
-        <v>91780</v>
+        <v>91818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425072</v>
+        <v>425256</v>
       </c>
       <c r="R15" t="n">
-        <v>6712273</v>
+        <v>6712203</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066769</v>
+        <v>131066782</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>91832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,42 +2083,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425267</v>
+        <v>425059</v>
       </c>
       <c r="R16" t="n">
-        <v>6712232</v>
+        <v>6712253</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2151,11 +2143,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,32 +2169,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066782</v>
+        <v>131066761</v>
       </c>
       <c r="B17" t="n">
-        <v>91831</v>
+        <v>91781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2204,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425059</v>
+        <v>425072</v>
       </c>
       <c r="R17" t="n">
-        <v>6712253</v>
+        <v>6712273</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2279,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131066768</v>
+        <v>131066769</v>
       </c>
       <c r="B18" t="n">
-        <v>91817</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2290,34 +2277,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425256</v>
+        <v>425267</v>
       </c>
       <c r="R18" t="n">
-        <v>6712203</v>
+        <v>6712232</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2350,6 +2345,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2379,7 @@
         <v>131066775</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>131066773</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066774</v>
+        <v>131066778</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>81235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,42 +2607,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425250</v>
+        <v>425336</v>
       </c>
       <c r="R21" t="n">
-        <v>6712265</v>
+        <v>6712202</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2675,11 +2667,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,7 +2696,7 @@
         <v>131066766</v>
       </c>
       <c r="B22" t="n">
-        <v>92188</v>
+        <v>92189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2803,10 +2790,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131066778</v>
+        <v>131066774</v>
       </c>
       <c r="B23" t="n">
-        <v>81234</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,34 +2801,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425336</v>
+        <v>425250</v>
       </c>
       <c r="R23" t="n">
-        <v>6712202</v>
+        <v>6712265</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2874,6 +2869,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2903,7 +2903,7 @@
         <v>131066786</v>
       </c>
       <c r="B24" t="n">
-        <v>83095</v>
+        <v>83096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>131066762</v>
       </c>
       <c r="B25" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>131066765</v>
       </c>
       <c r="B26" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>131066789</v>
       </c>
       <c r="B27" t="n">
-        <v>83221</v>
+        <v>83222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131066791</v>
       </c>
       <c r="B28" t="n">
-        <v>83221</v>
+        <v>83222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131066777</v>
       </c>
       <c r="B29" t="n">
-        <v>92236</v>
+        <v>92237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>131066776</v>
       </c>
       <c r="B30" t="n">
-        <v>80355</v>
+        <v>80356</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>131066772</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131066790</v>
+        <v>131066784</v>
       </c>
       <c r="B32" t="n">
-        <v>83221</v>
+        <v>83096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425164</v>
+        <v>425170</v>
       </c>
       <c r="R32" t="n">
-        <v>6712278</v>
+        <v>6712283</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131066767</v>
+        <v>131066790</v>
       </c>
       <c r="B33" t="n">
-        <v>91817</v>
+        <v>83222</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425259</v>
+        <v>425164</v>
       </c>
       <c r="R33" t="n">
-        <v>6712201</v>
+        <v>6712278</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131066784</v>
+        <v>131066767</v>
       </c>
       <c r="B34" t="n">
-        <v>83095</v>
+        <v>91818</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425170</v>
+        <v>425259</v>
       </c>
       <c r="R34" t="n">
-        <v>6712283</v>
+        <v>6712201</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -1076,53 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066771</v>
+        <v>131066787</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>80390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425297</v>
+        <v>425069</v>
       </c>
       <c r="R6" t="n">
-        <v>6712214</v>
+        <v>6712290</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1155,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,45 +1270,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066787</v>
+        <v>131066771</v>
       </c>
       <c r="B8" t="n">
-        <v>80390</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425069</v>
+        <v>425297</v>
       </c>
       <c r="R8" t="n">
-        <v>6712290</v>
+        <v>6712214</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2072,32 +2072,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066782</v>
+        <v>131066761</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425059</v>
+        <v>425072</v>
       </c>
       <c r="R16" t="n">
-        <v>6712253</v>
+        <v>6712273</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2169,32 +2169,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066761</v>
+        <v>131066782</v>
       </c>
       <c r="B17" t="n">
-        <v>91781</v>
+        <v>91832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425072</v>
+        <v>425059</v>
       </c>
       <c r="R17" t="n">
-        <v>6712273</v>
+        <v>6712253</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2596,10 +2596,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066778</v>
+        <v>131066774</v>
       </c>
       <c r="B21" t="n">
-        <v>81235</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,34 +2607,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425336</v>
+        <v>425250</v>
       </c>
       <c r="R21" t="n">
-        <v>6712202</v>
+        <v>6712265</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2667,6 +2675,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2693,32 +2706,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131066766</v>
+        <v>131066778</v>
       </c>
       <c r="B22" t="n">
-        <v>92189</v>
+        <v>81235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2741,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425069</v>
+        <v>425336</v>
       </c>
       <c r="R22" t="n">
-        <v>6712285</v>
+        <v>6712202</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2790,53 +2803,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131066774</v>
+        <v>131066766</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>92189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425250</v>
+        <v>425069</v>
       </c>
       <c r="R23" t="n">
-        <v>6712265</v>
+        <v>6712285</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2869,11 +2874,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,7 +2997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131066762</v>
+        <v>131066765</v>
       </c>
       <c r="B25" t="n">
         <v>91781</v>
@@ -3035,7 +3035,7 @@
         <v>425059</v>
       </c>
       <c r="R25" t="n">
-        <v>6712254</v>
+        <v>6712253</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131066765</v>
+        <v>131066762</v>
       </c>
       <c r="B26" t="n">
         <v>91781</v>
@@ -3132,7 +3132,7 @@
         <v>425059</v>
       </c>
       <c r="R26" t="n">
-        <v>6712253</v>
+        <v>6712254</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130766137</v>
+        <v>131066788</v>
       </c>
       <c r="B2" t="n">
-        <v>91808</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425065</v>
+        <v>425211</v>
       </c>
       <c r="R2" t="n">
-        <v>6712277</v>
+        <v>6712276</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,57 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130766153</v>
+        <v>131066789</v>
       </c>
       <c r="B3" t="n">
-        <v>80377</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425072</v>
+        <v>425178</v>
       </c>
       <c r="R3" t="n">
-        <v>6712283</v>
+        <v>6712289</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130766169</v>
+        <v>131066790</v>
       </c>
       <c r="B4" t="n">
-        <v>83089</v>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425089</v>
+        <v>425164</v>
       </c>
       <c r="R4" t="n">
-        <v>6712285</v>
+        <v>6712278</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130766140</v>
+        <v>131066791</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425067</v>
+        <v>425070</v>
       </c>
       <c r="R5" t="n">
-        <v>6712282</v>
+        <v>6712258</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1039,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066787</v>
+        <v>131066792</v>
       </c>
       <c r="B6" t="n">
-        <v>80390</v>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425069</v>
+        <v>425067</v>
       </c>
       <c r="R6" t="n">
-        <v>6712290</v>
+        <v>6712259</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1161,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066788</v>
+        <v>131887878</v>
       </c>
       <c r="B7" t="n">
-        <v>83222</v>
+        <v>92640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>483</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425211</v>
+        <v>425163</v>
       </c>
       <c r="R7" t="n">
-        <v>6712276</v>
+        <v>6712283</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1238,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1258,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131066771</v>
+        <v>131066778</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,42 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425297</v>
+        <v>425336</v>
       </c>
       <c r="R8" t="n">
-        <v>6712214</v>
+        <v>6712202</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1351,11 +1330,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1368,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131066770</v>
+        <v>130766137</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425323</v>
+        <v>425065</v>
       </c>
       <c r="R9" t="n">
-        <v>6712206</v>
+        <v>6712277</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1453,17 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1478,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131066783</v>
+        <v>130766139</v>
       </c>
       <c r="B10" t="n">
-        <v>83096</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425170</v>
+        <v>425085</v>
       </c>
       <c r="R10" t="n">
-        <v>6712292</v>
+        <v>6712306</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1555,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1575,44 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131066760</v>
+        <v>131066767</v>
       </c>
       <c r="B11" t="n">
-        <v>91781</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425281</v>
+        <v>425259</v>
       </c>
       <c r="R11" t="n">
-        <v>6712191</v>
+        <v>6712201</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1672,44 +1633,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131066781</v>
+        <v>131066768</v>
       </c>
       <c r="B12" t="n">
-        <v>83213</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425072</v>
+        <v>425256</v>
       </c>
       <c r="R12" t="n">
-        <v>6712273</v>
+        <v>6712203</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1769,44 +1730,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131066780</v>
+        <v>131066782</v>
       </c>
       <c r="B13" t="n">
-        <v>83213</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425163</v>
+        <v>425059</v>
       </c>
       <c r="R13" t="n">
-        <v>6712279</v>
+        <v>6712253</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1866,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131066792</v>
+        <v>130766155</v>
       </c>
       <c r="B14" t="n">
-        <v>83222</v>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425067</v>
+        <v>425085</v>
       </c>
       <c r="R14" t="n">
-        <v>6712259</v>
+        <v>6712306</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1943,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1963,22 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131066768</v>
+        <v>130766169</v>
       </c>
       <c r="B15" t="n">
-        <v>91818</v>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425256</v>
+        <v>425089</v>
       </c>
       <c r="R15" t="n">
-        <v>6712203</v>
+        <v>6712285</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2040,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2060,44 +2021,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131066761</v>
+        <v>131066783</v>
       </c>
       <c r="B16" t="n">
-        <v>91781</v>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2107,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425072</v>
+        <v>425170</v>
       </c>
       <c r="R16" t="n">
-        <v>6712273</v>
+        <v>6712292</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2157,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131066782</v>
+        <v>131066784</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2180,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2204,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425059</v>
+        <v>425170</v>
       </c>
       <c r="R17" t="n">
-        <v>6712253</v>
+        <v>6712283</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2254,22 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131066769</v>
+        <v>131066785</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,42 +2238,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425267</v>
+        <v>425136</v>
       </c>
       <c r="R18" t="n">
-        <v>6712232</v>
+        <v>6712265</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2347,11 +2300,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2364,22 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131066775</v>
+        <v>131066786</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2387,42 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425244</v>
+        <v>425073</v>
       </c>
       <c r="R19" t="n">
-        <v>6712292</v>
+        <v>6712276</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2457,11 +2397,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2474,68 +2409,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131066773</v>
+        <v>131887953</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>92655</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1965</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425271</v>
+        <v>425164</v>
       </c>
       <c r="R20" t="n">
-        <v>6712264</v>
+        <v>6712287</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2559,17 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2584,65 +2506,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131066774</v>
+        <v>131066766</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>92281</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425250</v>
+        <v>425069</v>
       </c>
       <c r="R21" t="n">
-        <v>6712265</v>
+        <v>6712285</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2677,11 +2591,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2694,22 +2603,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131066778</v>
+        <v>131066776</v>
       </c>
       <c r="B22" t="n">
-        <v>81235</v>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425336</v>
+        <v>425069</v>
       </c>
       <c r="R22" t="n">
-        <v>6712202</v>
+        <v>6712285</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2791,57 +2700,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131066766</v>
+        <v>130766131</v>
       </c>
       <c r="B23" t="n">
-        <v>92189</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425069</v>
+        <v>425145</v>
       </c>
       <c r="R23" t="n">
-        <v>6712285</v>
+        <v>6712296</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2868,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2888,57 +2797,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131066786</v>
+        <v>130766132</v>
       </c>
       <c r="B24" t="n">
-        <v>83096</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425073</v>
+        <v>425143</v>
       </c>
       <c r="R24" t="n">
-        <v>6712276</v>
+        <v>6712315</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2965,12 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2985,22 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131066765</v>
+        <v>130766136</v>
       </c>
       <c r="B25" t="n">
-        <v>91781</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3028,14 +2937,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425059</v>
+        <v>425084</v>
       </c>
       <c r="R25" t="n">
-        <v>6712253</v>
+        <v>6712300</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3062,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3082,22 +2991,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131066762</v>
+        <v>131066760</v>
       </c>
       <c r="B26" t="n">
-        <v>91781</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3129,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425059</v>
+        <v>425281</v>
       </c>
       <c r="R26" t="n">
-        <v>6712254</v>
+        <v>6712191</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3179,44 +3088,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131066789</v>
+        <v>131066761</v>
       </c>
       <c r="B27" t="n">
-        <v>83222</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3226,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425178</v>
+        <v>425072</v>
       </c>
       <c r="R27" t="n">
-        <v>6712289</v>
+        <v>6712273</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3276,44 +3185,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131066791</v>
+        <v>131066762</v>
       </c>
       <c r="B28" t="n">
-        <v>83222</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3323,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425070</v>
+        <v>425059</v>
       </c>
       <c r="R28" t="n">
-        <v>6712258</v>
+        <v>6712254</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3373,44 +3282,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131066777</v>
+        <v>131066765</v>
       </c>
       <c r="B29" t="n">
-        <v>92237</v>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3420,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425259</v>
+        <v>425059</v>
       </c>
       <c r="R29" t="n">
-        <v>6712201</v>
+        <v>6712253</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3464,51 +3373,50 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131066776</v>
+        <v>131066780</v>
       </c>
       <c r="B30" t="n">
-        <v>80356</v>
+        <v>83290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425069</v>
+        <v>425163</v>
       </c>
       <c r="R30" t="n">
-        <v>6712285</v>
+        <v>6712279</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3568,65 +3476,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131066772</v>
+        <v>131066781</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>83290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425301</v>
+        <v>425072</v>
       </c>
       <c r="R31" t="n">
-        <v>6712219</v>
+        <v>6712273</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3661,11 +3561,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3678,54 +3573,54 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131066784</v>
+        <v>130766153</v>
       </c>
       <c r="B32" t="n">
-        <v>83096</v>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425170</v>
+        <v>425072</v>
       </c>
       <c r="R32" t="n">
         <v>6712283</v>
@@ -3755,12 +3650,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,44 +3670,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131066790</v>
+        <v>131066787</v>
       </c>
       <c r="B33" t="n">
-        <v>83222</v>
+        <v>80467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3822,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425164</v>
+        <v>425069</v>
       </c>
       <c r="R33" t="n">
-        <v>6712278</v>
+        <v>6712290</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3872,22 +3767,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131066767</v>
+        <v>130766174</v>
       </c>
       <c r="B34" t="n">
-        <v>91818</v>
+        <v>57874</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,34 +3790,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425259</v>
+        <v>425032</v>
       </c>
       <c r="R34" t="n">
-        <v>6712201</v>
+        <v>6712262</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3949,12 +3848,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Den flög förbi och satte sig i ett träd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3969,66 +3873,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131082611</v>
+        <v>130766140</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>425297</v>
+        <v>425067</v>
       </c>
       <c r="R35" t="n">
-        <v>6712214</v>
+        <v>6712282</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4055,12 +3958,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4069,73 +3977,71 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131082603</v>
+        <v>130766141</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425301</v>
+        <v>425150</v>
       </c>
       <c r="R36" t="n">
-        <v>6712219</v>
+        <v>6712304</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4162,12 +4068,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4176,67 +4087,74 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131887878</v>
+        <v>130766142</v>
       </c>
       <c r="B37" t="n">
-        <v>92556</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>483</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425163</v>
+        <v>425142</v>
       </c>
       <c r="R37" t="n">
-        <v>6712283</v>
+        <v>6712318</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4260,12 +4178,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4292,48 +4215,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131887953</v>
+        <v>130766152</v>
       </c>
       <c r="B38" t="n">
-        <v>92570</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1965</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>425164</v>
+        <v>425080</v>
       </c>
       <c r="R38" t="n">
-        <v>6712287</v>
+        <v>6712311</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4357,12 +4288,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,6 +4322,1395 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131066769</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>425267</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6712232</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131066770</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>425323</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6712206</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131066771</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>425297</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6712214</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131066772</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>425301</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6712219</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131066773</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>425271</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6712264</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131066774</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>425250</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6712265</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131066775</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>425244</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6712292</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131082603</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>425301</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6712219</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131082611</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>425297</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6712214</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131887879</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>425060</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6712208</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130766158</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Östra utsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>425143</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6712305</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130766159</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Östra utsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>425088</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6712301</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131066777</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>425259</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6712201</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131066780</v>
+        <v>131887920</v>
       </c>
       <c r="B30" t="n">
-        <v>83290</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,13 +3426,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425163</v>
+        <v>425130</v>
       </c>
       <c r="R30" t="n">
-        <v>6712279</v>
+        <v>6712317</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3456,12 +3456,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3470,6 +3475,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3488,7 +3494,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131066781</v>
+        <v>131066780</v>
       </c>
       <c r="B31" t="n">
         <v>83290</v>
@@ -3523,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425072</v>
+        <v>425163</v>
       </c>
       <c r="R31" t="n">
-        <v>6712273</v>
+        <v>6712279</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3585,10 +3591,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130766153</v>
+        <v>131066781</v>
       </c>
       <c r="B32" t="n">
-        <v>80461</v>
+        <v>83290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,34 +3602,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
         <v>425072</v>
       </c>
       <c r="R32" t="n">
-        <v>6712283</v>
+        <v>6712273</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3650,12 +3656,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3682,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131066787</v>
+        <v>130766153</v>
       </c>
       <c r="B33" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,34 +3699,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425069</v>
+        <v>425072</v>
       </c>
       <c r="R33" t="n">
-        <v>6712290</v>
+        <v>6712283</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3747,12 +3753,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3779,49 +3785,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130766174</v>
+        <v>131066787</v>
       </c>
       <c r="B34" t="n">
-        <v>57874</v>
+        <v>80467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100001</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425032</v>
+        <v>425069</v>
       </c>
       <c r="R34" t="n">
-        <v>6712262</v>
+        <v>6712290</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3848,17 +3850,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Den flög förbi och satte sig i ett träd.</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3885,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130766140</v>
+        <v>130766174</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>57874</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3896,16 +3893,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3916,11 +3913,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3928,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>425067</v>
+        <v>425032</v>
       </c>
       <c r="R35" t="n">
-        <v>6712282</v>
+        <v>6712262</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3968,7 +3961,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Den flög förbi och satte sig i ett träd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3995,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130766141</v>
+        <v>130766140</v>
       </c>
       <c r="B36" t="n">
         <v>57953</v>
@@ -4038,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425150</v>
+        <v>425067</v>
       </c>
       <c r="R36" t="n">
-        <v>6712304</v>
+        <v>6712282</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4105,7 +4098,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130766142</v>
+        <v>130766141</v>
       </c>
       <c r="B37" t="n">
         <v>57953</v>
@@ -4138,7 +4131,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4148,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425142</v>
+        <v>425150</v>
       </c>
       <c r="R37" t="n">
-        <v>6712318</v>
+        <v>6712304</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4215,7 +4208,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130766152</v>
+        <v>130766142</v>
       </c>
       <c r="B38" t="n">
         <v>57953</v>
@@ -4258,10 +4251,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>425080</v>
+        <v>425142</v>
       </c>
       <c r="R38" t="n">
-        <v>6712311</v>
+        <v>6712318</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4325,7 +4318,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131066769</v>
+        <v>130766152</v>
       </c>
       <c r="B39" t="n">
         <v>57953</v>
@@ -4358,20 +4351,20 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425267</v>
+        <v>425080</v>
       </c>
       <c r="R39" t="n">
-        <v>6712232</v>
+        <v>6712311</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4398,17 +4391,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4435,7 +4428,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131066770</v>
+        <v>131066769</v>
       </c>
       <c r="B40" t="n">
         <v>57953</v>
@@ -4478,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425323</v>
+        <v>425267</v>
       </c>
       <c r="R40" t="n">
-        <v>6712206</v>
+        <v>6712232</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4545,7 +4538,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131066771</v>
+        <v>131066770</v>
       </c>
       <c r="B41" t="n">
         <v>57953</v>
@@ -4588,10 +4581,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425297</v>
+        <v>425323</v>
       </c>
       <c r="R41" t="n">
-        <v>6712214</v>
+        <v>6712206</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4655,7 +4648,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131066772</v>
+        <v>131066771</v>
       </c>
       <c r="B42" t="n">
         <v>57953</v>
@@ -4698,10 +4691,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>425301</v>
+        <v>425297</v>
       </c>
       <c r="R42" t="n">
-        <v>6712219</v>
+        <v>6712214</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4765,7 +4758,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131066773</v>
+        <v>131066772</v>
       </c>
       <c r="B43" t="n">
         <v>57953</v>
@@ -4808,10 +4801,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425271</v>
+        <v>425301</v>
       </c>
       <c r="R43" t="n">
-        <v>6712264</v>
+        <v>6712219</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4875,7 +4868,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131066774</v>
+        <v>131066773</v>
       </c>
       <c r="B44" t="n">
         <v>57953</v>
@@ -4918,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425250</v>
+        <v>425271</v>
       </c>
       <c r="R44" t="n">
-        <v>6712265</v>
+        <v>6712264</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -4985,7 +4978,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131066775</v>
+        <v>131066774</v>
       </c>
       <c r="B45" t="n">
         <v>57953</v>
@@ -5028,10 +5021,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425244</v>
+        <v>425250</v>
       </c>
       <c r="R45" t="n">
-        <v>6712292</v>
+        <v>6712265</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5095,41 +5088,40 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131082603</v>
+        <v>131066775</v>
       </c>
       <c r="B46" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5139,10 +5131,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>425301</v>
+        <v>425244</v>
       </c>
       <c r="R46" t="n">
-        <v>6712219</v>
+        <v>6712292</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5177,13 +5169,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5202,7 +5198,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131082611</v>
+        <v>131082603</v>
       </c>
       <c r="B47" t="n">
         <v>5179</v>
@@ -5236,7 +5232,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5246,10 +5242,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425297</v>
+        <v>425301</v>
       </c>
       <c r="R47" t="n">
-        <v>6712214</v>
+        <v>6712219</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5309,10 +5305,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131887879</v>
+        <v>131082611</v>
       </c>
       <c r="B48" t="n">
-        <v>57165</v>
+        <v>5179</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5320,29 +5316,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102613</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5352,13 +5349,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425060</v>
+        <v>425297</v>
       </c>
       <c r="R48" t="n">
-        <v>6712208</v>
+        <v>6712214</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5382,12 +5379,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5396,6 +5393,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5414,51 +5412,56 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130766158</v>
+        <v>131887879</v>
       </c>
       <c r="B49" t="n">
-        <v>92329</v>
+        <v>57165</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6040186</v>
+        <v>102613</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425143</v>
+        <v>425060</v>
       </c>
       <c r="R49" t="n">
-        <v>6712305</v>
+        <v>6712208</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5482,12 +5485,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5496,7 +5499,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5515,7 +5517,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130766159</v>
+        <v>130766158</v>
       </c>
       <c r="B50" t="n">
         <v>92329</v>
@@ -5553,10 +5555,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425088</v>
+        <v>425143</v>
       </c>
       <c r="R50" t="n">
-        <v>6712301</v>
+        <v>6712305</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5616,7 +5618,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131066777</v>
+        <v>130766159</v>
       </c>
       <c r="B51" t="n">
         <v>92329</v>
@@ -5645,16 +5647,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>425259</v>
+        <v>425088</v>
       </c>
       <c r="R51" t="n">
-        <v>6712201</v>
+        <v>6712301</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5681,12 +5686,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5711,6 +5716,104 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131066777</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>425259</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6712201</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1480-2026 artfynd.xlsx
+++ b/artfynd/A 1480-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066789</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066790</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066791</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066792</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066778</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766137</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766139</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066768</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066782</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766155</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766169</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066784</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066785</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066786</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887953</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066766</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066776</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766131</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766132</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766136</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066760</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066761</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066762</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066765</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3491,6 +3636,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887920</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3588,6 +3738,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066780</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3685,6 +3840,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066781</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3782,6 +3942,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766153</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3879,6 +4044,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066787</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3985,6 +4155,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766174</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4095,6 +4270,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766140</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4205,6 +4385,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766141</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4315,6 +4500,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766142</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4425,6 +4615,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766152</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4535,6 +4730,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066769</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4645,6 +4845,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066770</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4755,6 +4960,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066771</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4865,6 +5075,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066772</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4975,6 +5190,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066773</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5085,6 +5305,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066774</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5195,6 +5420,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066775</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5302,6 +5532,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082603</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5409,6 +5644,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082611</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5514,6 +5754,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887879</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5615,6 +5860,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766158</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5716,6 +5966,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766159</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5814,8 +6069,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>